--- a/roadmap.xlsx
+++ b/roadmap.xlsx
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -364,16 +364,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1010,7 +1005,7 @@
       <c r="L4" s="11" t="n"/>
       <c r="M4" s="11" t="n"/>
       <c r="N4" s="11" t="n"/>
-      <c r="O4" s="11" t="n"/>
+      <c r="O4" s="12" t="n"/>
       <c r="P4" s="11" t="n"/>
       <c r="Q4" s="11" t="n"/>
       <c r="R4" s="11" t="n"/>
@@ -1051,7 +1046,7 @@
       <c r="L5" s="11" t="n"/>
       <c r="M5" s="11" t="n"/>
       <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
+      <c r="O5" s="12" t="n"/>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="11" t="n"/>
       <c r="R5" s="11" t="n"/>
@@ -1131,7 +1126,7 @@
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>2 нед, 10 чд</t>
         </is>
@@ -1141,7 +1136,7 @@
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
       <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
+      <c r="S7" s="12" t="n"/>
       <c r="T7" s="11" t="n"/>
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="11" t="n"/>
@@ -1172,7 +1167,7 @@
       <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
       <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="M8" s="19" t="n"/>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="15" t="inlineStr">
         <is>
@@ -1182,7 +1177,7 @@
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="11" t="n"/>
       <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
+      <c r="S8" s="12" t="n"/>
       <c r="T8" s="11" t="n"/>
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="11" t="n"/>
@@ -1213,7 +1208,7 @@
       <c r="J9" s="11" t="n"/>
       <c r="K9" s="11" t="n"/>
       <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="M9" s="19" t="n"/>
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="17" t="inlineStr">
@@ -1260,7 +1255,7 @@
       <c r="L10" s="11" t="n"/>
       <c r="M10" s="11" t="n"/>
       <c r="N10" s="11" t="n"/>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>4 нед, 20 чд</t>
         </is>
@@ -1276,7 +1271,7 @@
       <c r="X10" s="11" t="n"/>
       <c r="Y10" s="11" t="n"/>
       <c r="Z10" s="11" t="n"/>
-      <c r="AA10" s="11" t="n"/>
+      <c r="AA10" s="12" t="n"/>
       <c r="AB10" s="11" t="n"/>
       <c r="AC10" s="11" t="n"/>
       <c r="AD10" s="11" t="n"/>
@@ -1301,7 +1296,7 @@
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n"/>
+      <c r="O11" s="19" t="n"/>
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -1317,7 +1312,7 @@
       <c r="X11" s="11" t="n"/>
       <c r="Y11" s="11" t="n"/>
       <c r="Z11" s="11" t="n"/>
-      <c r="AA11" s="11" t="n"/>
+      <c r="AA11" s="12" t="n"/>
       <c r="AB11" s="11" t="n"/>
       <c r="AC11" s="11" t="n"/>
       <c r="AD11" s="11" t="n"/>
@@ -1342,7 +1337,7 @@
       <c r="L12" s="11" t="n"/>
       <c r="M12" s="11" t="n"/>
       <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
+      <c r="O12" s="19" t="n"/>
       <c r="P12" s="11" t="n"/>
       <c r="Q12" s="11" t="n"/>
       <c r="R12" s="11" t="n"/>
@@ -1397,7 +1392,7 @@
       <c r="V13" s="11" t="n"/>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="11" t="n"/>
-      <c r="Y13" s="19" t="inlineStr">
+      <c r="Y13" s="9" t="inlineStr">
         <is>
           <t>2 нед, 10 чд</t>
         </is>
@@ -1438,7 +1433,7 @@
       <c r="V14" s="11" t="n"/>
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
-      <c r="Y14" s="11" t="n"/>
+      <c r="Y14" s="19" t="n"/>
       <c r="Z14" s="11" t="n"/>
       <c r="AA14" s="15" t="inlineStr">
         <is>
@@ -1479,10 +1474,10 @@
       <c r="V15" s="11" t="n"/>
       <c r="W15" s="11" t="n"/>
       <c r="X15" s="11" t="n"/>
-      <c r="Y15" s="11" t="n"/>
+      <c r="Y15" s="19" t="n"/>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="11" t="n"/>
-      <c r="AB15" s="20" t="inlineStr">
+      <c r="AB15" s="17" t="inlineStr">
         <is>
           <t>4 нед, 30 чд</t>
         </is>
@@ -1492,70 +1487,70 @@
       <c r="AE15" s="18" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Легенда:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>◆ выполнено / факт</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>◇ план / под вопросом</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>работы (разработка)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>аналитика (SDD)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>тестирование</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>оценка т/з</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>отпуск</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>⚑ старт</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>⚑ финиш</t>
         </is>
